--- a/data/evaluation_results_4.xlsx
+++ b/data/evaluation_results_4.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -522,27 +516,24 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student would be detention or a warning, possibly followed by a parent contact or a meeting to discuss the infraction.</t>
+          <t>The most likely consequence for the student would be detention or a warning, possibly followed by a parent contact or a meeting with the school administration.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:32.796159+00:00</t>
+          <t>2026-10-22T04:32:21.308110+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.4744441210000332</v>
+        <v>0.3948657300002196</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.4910817580000639</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -563,27 +554,24 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student would be detention or a warning, possibly followed by a parent contact or a meeting to discuss the infraction.</t>
+          <t>The most likely consequence for the student would be detention or a warning, possibly followed by a parent contact or a meeting with the school administration.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:33.287531+00:00</t>
+          <t>2026-10-22T04:32:21.703244+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.399854742999878</v>
+        <v>0.4873751909999555</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.4121184620000804</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -604,27 +592,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student would be detention or a warning, followed by a parent contact or meeting.</t>
+          <t>The most likely consequence for the student would be detention or a warning, possibly followed by a parent contact or a meeting with the school administration.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:33.699877+00:00</t>
+          <t>2026-10-22T04:32:22.190831+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.3555138220001481</v>
+        <v>0.3710878850001791</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.3660903110001072</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -660,22 +645,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:34.066196+00:00</t>
+          <t>2026-10-22T04:32:22.562122+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.332248574999994</v>
+        <v>1.376099945000078</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.348589838999942</v>
+        <v>75</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J5" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -711,22 +693,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:35.415063+00:00</t>
+          <t>2026-10-22T04:32:23.938472+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.338836141000002</v>
+        <v>1.329076721999627</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.356544482000118</v>
+        <v>75</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J6" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -747,9 +726,8 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>To solve this problem, let's use algebra. 
-Let x be the cost of the ball. 
-Since the bat costs $1.00 more than the ball, the bat costs x + $1.00.
+          <t>To find the cost of the ball, let's denote the cost of the ball as x.
+Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
 The total cost of the bat and the ball together is $1.10, so we can set up the equation:
 x + (x + $1.00) = $1.10
 Combine like terms:
@@ -758,27 +736,24 @@
 2x = $0.10
 Divide both sides by 2:
 x = $0.05
-So, the ball costs $0.05.</t>
+The ball costs $0.05.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:36.771819+00:00</t>
+          <t>2026-10-22T04:32:25.267772+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.674616417999914</v>
+        <v>1.614300655000079</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.693808094999895</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -802,29 +777,28 @@
           <t>To find the number of days, we need to calculate the net progress of the snail each day.
 The snail climbs 3 feet up and slips back 2 feet, so the net progress is:
 3 - 2 = 1 foot
-Since the well is 20 feet deep, we can divide the depth by the net progress to find the number of days:
-20 / 1 = 20 days
-However, on the 20th day, the snail will climb 3 feet and reach the top of the well. So, it will take 20 days for the snail to reach the top of the well.</t>
+Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
+To find the number of days, we can divide the depth of the well by the net progress:
+20 feet / 1 foot = 20 days
+However, this calculation assumes that the snail will climb 3 feet on the 20th day and reach the top. But since the snail slips back 2 feet at night, it will only reach the top on the 20th day if it climbs 3 feet on the 20th day and doesn't slip back.
+So, the correct answer is 20 days.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:38.465933+00:00</t>
+          <t>2026-10-22T04:32:26.882301+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.307092901000033</v>
+        <v>1.697227936999752</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.325312253999982</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>188</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -845,31 +819,30 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>To solve this, let's break it down:
-The snail climbs 3 feet up and slips 2 feet back, so it effectively moves 1 foot up each day.
-Since the well is 20 feet deep, the snail needs to cover 20 feet. 
+          <t>To solve this problem, we need to calculate the net progress of the snail each day.
+The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress each day is:
+3 (up) - 2 (down) = 1 foot
+Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
+To find the number of days, we can divide the total depth by the net progress:
 20 feet / 1 foot per day = 20 days
-However, on the 20th day, the snail will climb 3 feet and reach the top, so it will take 20 days + 1 day = 21 days.</t>
+However, on the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back 2 feet because it's already at the top. So, the correct answer is 20 days.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:39.791492+00:00</t>
+          <t>2026-10-22T04:32:28.579870+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.046533182000076</v>
+        <v>1.641785195000011</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.062256059999982</v>
+        <v>97</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>175</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -891,35 +864,33 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>To solve this, let's break it down:
-The snail climbs 3 feet up and slips 2 feet back, so it effectively moves 1 foot up each day.
-Since the well is 20 feet deep, the snail needs to cover 20 feet. 
-To find the number of days, divide the total depth by the daily progress:
+Day 1: Snail climbs 3 feet, so it's at 3 feet. At night, it slips back 2 feet, so it's at 1 foot.
+Day 2: Snail climbs 3 feet, so it's at 4 feet. At night, it slips back 2 feet, so it's at 2 feet.
+Day 3: Snail climbs 3 feet, so it's at 5 feet. At night, it slips back 2 feet, so it's at 3 feet.
+Notice a pattern? The snail effectively climbs 1 foot per day.
+Since the well is 20 feet deep, and the snail climbs 1 foot per day, it will take:
 20 feet / 1 foot per day = 20 days
-However, on the 20th day, the snail will climb 3 feet and reach the top, so it won't slip back. 
-Therefore, it will take the snail 20 days to reach the top of the well.</t>
+However, on the 20th day, the snail will climb 3 feet and reach the top of the well, so it will actually take 20 days + 1 day = 21 days.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:40.853955+00:00</t>
+          <t>2026-10-22T04:32:30.221917+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.262427672000058</v>
+        <v>1.932188098999632</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.283520522000117</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -991,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1019,10 +990,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 1.174,
-  "median_latency": 1.283,
+  "median_input": 76,
+  "median_output": 145,
+  "median_latency": 1.635,
   "correct_frequency": 0.8333333333333334,
-  "misinformation_frequency": 0
+  "misinformation_frequency": 0,
+  "relevance_frequency": 1
 }</t>
         </is>
       </c>
@@ -1030,45 +1003,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.174</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.283</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.635</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1106,7 +1099,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:00:43.335243+00:00</t>
+          <t>2026-10-22T04:32:33.600335+00:00</t>
         </is>
       </c>
     </row>
